--- a/artfynd/A 41505-2024 artfynd.xlsx
+++ b/artfynd/A 41505-2024 artfynd.xlsx
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120223955</v>
+        <v>120222626</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,42 +1602,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566345</v>
+        <v>566559</v>
       </c>
       <c r="R10" t="n">
-        <v>7041782</v>
+        <v>7041473</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,7 +1702,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120222384</v>
+        <v>120223955</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1741,19 +1737,19 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566537</v>
+        <v>566345</v>
       </c>
       <c r="R11" t="n">
-        <v>7041443</v>
+        <v>7041782</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1791,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120222626</v>
+        <v>120222384</v>
       </c>
       <c r="B12" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,38 +1830,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566559</v>
+        <v>566537</v>
       </c>
       <c r="R12" t="n">
-        <v>7041473</v>
+        <v>7041443</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 41505-2024 artfynd.xlsx
+++ b/artfynd/A 41505-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120223831</v>
+        <v>120222972</v>
       </c>
       <c r="B4" t="n">
-        <v>90582</v>
+        <v>56522</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,41 +911,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566397</v>
+        <v>566530</v>
       </c>
       <c r="R4" t="n">
-        <v>7041615</v>
+        <v>7041605</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120222972</v>
+        <v>120223831</v>
       </c>
       <c r="B5" t="n">
-        <v>56522</v>
+        <v>90582</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,46 +1028,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566530</v>
+        <v>566397</v>
       </c>
       <c r="R5" t="n">
-        <v>7041605</v>
+        <v>7041615</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120222626</v>
+        <v>120222384</v>
       </c>
       <c r="B10" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,38 +1602,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566559</v>
+        <v>566537</v>
       </c>
       <c r="R10" t="n">
-        <v>7041473</v>
+        <v>7041443</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120223955</v>
+        <v>120222626</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,42 +1718,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566345</v>
+        <v>566559</v>
       </c>
       <c r="R11" t="n">
-        <v>7041782</v>
+        <v>7041473</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,7 +1818,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120222384</v>
+        <v>120223955</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1853,19 +1853,19 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566537</v>
+        <v>566345</v>
       </c>
       <c r="R12" t="n">
-        <v>7041443</v>
+        <v>7041782</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2985,10 +2985,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120223457</v>
+        <v>120222471</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2997,42 +2997,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566452</v>
+        <v>566555</v>
       </c>
       <c r="R22" t="n">
-        <v>7041743</v>
+        <v>7041449</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3064,7 +3060,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3074,7 +3070,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3101,10 +3097,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120222471</v>
+        <v>120222649</v>
       </c>
       <c r="B23" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3117,34 +3113,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566555</v>
+        <v>566556</v>
       </c>
       <c r="R23" t="n">
-        <v>7041449</v>
+        <v>7041534</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3176,7 +3177,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3186,7 +3187,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3201,22 +3207,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120222649</v>
+        <v>120223457</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3225,43 +3231,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566556</v>
+        <v>566452</v>
       </c>
       <c r="R24" t="n">
-        <v>7041534</v>
+        <v>7041743</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3293,7 +3298,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3303,12 +3308,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3323,12 +3323,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 41505-2024 artfynd.xlsx
+++ b/artfynd/A 41505-2024 artfynd.xlsx
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120222384</v>
+        <v>120222626</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,42 +1602,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566537</v>
+        <v>566559</v>
       </c>
       <c r="R10" t="n">
-        <v>7041443</v>
+        <v>7041473</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120222626</v>
+        <v>120223955</v>
       </c>
       <c r="B11" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,38 +1714,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566559</v>
+        <v>566345</v>
       </c>
       <c r="R11" t="n">
-        <v>7041473</v>
+        <v>7041782</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,7 +1818,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120223955</v>
+        <v>120222384</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1853,19 +1853,19 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566345</v>
+        <v>566537</v>
       </c>
       <c r="R12" t="n">
-        <v>7041782</v>
+        <v>7041443</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 41505-2024 artfynd.xlsx
+++ b/artfynd/A 41505-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120222972</v>
+        <v>120223831</v>
       </c>
       <c r="B4" t="n">
-        <v>56522</v>
+        <v>90582</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,46 +911,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566530</v>
+        <v>566397</v>
       </c>
       <c r="R4" t="n">
-        <v>7041605</v>
+        <v>7041615</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120223831</v>
+        <v>120222972</v>
       </c>
       <c r="B5" t="n">
-        <v>90582</v>
+        <v>56522</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,41 +1023,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566397</v>
+        <v>566530</v>
       </c>
       <c r="R5" t="n">
-        <v>7041615</v>
+        <v>7041605</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120222626</v>
+        <v>120222384</v>
       </c>
       <c r="B10" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,38 +1602,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566559</v>
+        <v>566537</v>
       </c>
       <c r="R10" t="n">
-        <v>7041473</v>
+        <v>7041443</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120223955</v>
+        <v>120222626</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,42 +1718,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566345</v>
+        <v>566559</v>
       </c>
       <c r="R11" t="n">
-        <v>7041782</v>
+        <v>7041473</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,7 +1818,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120222384</v>
+        <v>120223955</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1853,19 +1853,19 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566537</v>
+        <v>566345</v>
       </c>
       <c r="R12" t="n">
-        <v>7041443</v>
+        <v>7041782</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2985,10 +2985,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120222471</v>
+        <v>120223457</v>
       </c>
       <c r="B22" t="n">
-        <v>90562</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2997,38 +2997,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566555</v>
+        <v>566452</v>
       </c>
       <c r="R22" t="n">
-        <v>7041449</v>
+        <v>7041743</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3060,7 +3064,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3070,7 +3074,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3097,10 +3101,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120222649</v>
+        <v>120222471</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3113,39 +3117,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566556</v>
+        <v>566555</v>
       </c>
       <c r="R23" t="n">
-        <v>7041534</v>
+        <v>7041449</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3177,7 +3176,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3187,12 +3186,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3207,22 +3201,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120223457</v>
+        <v>120222649</v>
       </c>
       <c r="B24" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3231,42 +3225,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566452</v>
+        <v>566556</v>
       </c>
       <c r="R24" t="n">
-        <v>7041743</v>
+        <v>7041534</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3298,7 +3293,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3308,7 +3303,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3323,12 +3323,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 41505-2024 artfynd.xlsx
+++ b/artfynd/A 41505-2024 artfynd.xlsx
@@ -1590,7 +1590,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120222384</v>
+        <v>120223955</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1625,19 +1625,19 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566537</v>
+        <v>566345</v>
       </c>
       <c r="R10" t="n">
-        <v>7041443</v>
+        <v>7041782</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1818,7 +1818,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120223955</v>
+        <v>120222384</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1853,19 +1853,19 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566345</v>
+        <v>566537</v>
       </c>
       <c r="R12" t="n">
-        <v>7041782</v>
+        <v>7041443</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 41505-2024 artfynd.xlsx
+++ b/artfynd/A 41505-2024 artfynd.xlsx
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120223955</v>
+        <v>120222626</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>90846</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,42 +1602,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566345</v>
+        <v>566559</v>
       </c>
       <c r="R10" t="n">
-        <v>7041782</v>
+        <v>7041473</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120222626</v>
+        <v>120222384</v>
       </c>
       <c r="B11" t="n">
-        <v>90846</v>
+        <v>97907</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,38 +1714,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566559</v>
+        <v>566537</v>
       </c>
       <c r="R11" t="n">
-        <v>7041473</v>
+        <v>7041443</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,7 +1818,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120222384</v>
+        <v>120223955</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1853,19 +1853,19 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566537</v>
+        <v>566345</v>
       </c>
       <c r="R12" t="n">
-        <v>7041443</v>
+        <v>7041782</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 41505-2024 artfynd.xlsx
+++ b/artfynd/A 41505-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120223099</v>
+        <v>120223202</v>
       </c>
       <c r="B2" t="n">
-        <v>91005</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566497</v>
+        <v>566493</v>
       </c>
       <c r="R2" t="n">
-        <v>7041610</v>
+        <v>7041714</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120223384</v>
+        <v>120222893</v>
       </c>
       <c r="B3" t="n">
-        <v>91005</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566465</v>
+        <v>566554</v>
       </c>
       <c r="R3" t="n">
-        <v>7041759</v>
+        <v>7041587</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120223831</v>
+        <v>120222653</v>
       </c>
       <c r="B4" t="n">
-        <v>90582</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,38 +916,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566397</v>
+        <v>566557</v>
       </c>
       <c r="R4" t="n">
-        <v>7041615</v>
+        <v>7041495</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120222972</v>
+        <v>120223736</v>
       </c>
       <c r="B5" t="n">
-        <v>56522</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,46 +1032,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566530</v>
+        <v>566434</v>
       </c>
       <c r="R5" t="n">
-        <v>7041605</v>
+        <v>7041848</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120222380</v>
+        <v>120222506</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>57473</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,34 +1153,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566570</v>
+        <v>566564</v>
       </c>
       <c r="R6" t="n">
-        <v>7041464</v>
+        <v>7041444</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,22 +1246,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120222949</v>
+        <v>120222380</v>
       </c>
       <c r="B7" t="n">
-        <v>56514</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,16 +1274,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1278,26 +1291,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566482</v>
+        <v>566570</v>
       </c>
       <c r="R7" t="n">
-        <v>7041546</v>
+        <v>7041464</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1343,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,22 +1363,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120222990</v>
+        <v>120222579</v>
       </c>
       <c r="B8" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,34 +1391,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566475</v>
+        <v>566558</v>
       </c>
       <c r="R8" t="n">
-        <v>7041565</v>
+        <v>7041464</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1465,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120222903</v>
+        <v>120222384</v>
       </c>
       <c r="B9" t="n">
-        <v>82305</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,38 +1509,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566505</v>
+        <v>566537</v>
       </c>
       <c r="R9" t="n">
-        <v>7041563</v>
+        <v>7041443</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1576,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1586,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120222626</v>
+        <v>120222763</v>
       </c>
       <c r="B10" t="n">
-        <v>90846</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,21 +1629,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1653,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566559</v>
+        <v>566538</v>
       </c>
       <c r="R10" t="n">
-        <v>7041473</v>
+        <v>7041535</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1688,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1698,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,22 +1718,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120222384</v>
+        <v>120223345</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,42 +1742,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566537</v>
+        <v>566473</v>
       </c>
       <c r="R11" t="n">
-        <v>7041443</v>
+        <v>7041726</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,7 +1805,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,7 +1815,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120223955</v>
+        <v>120223599</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>91246</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,38 +1858,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566345</v>
+        <v>566435</v>
       </c>
       <c r="R12" t="n">
-        <v>7041782</v>
+        <v>7041764</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,7 +1917,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1927,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,10 +1954,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120222763</v>
+        <v>120223955</v>
       </c>
       <c r="B13" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,38 +1966,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566538</v>
+        <v>566345</v>
       </c>
       <c r="R13" t="n">
-        <v>7041535</v>
+        <v>7041782</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,7 +2033,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,12 +2043,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,22 +2058,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120222579</v>
+        <v>120222408</v>
       </c>
       <c r="B14" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2096,10 +2115,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566558</v>
+        <v>566528</v>
       </c>
       <c r="R14" t="n">
-        <v>7041464</v>
+        <v>7041423</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,7 +2150,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,12 +2160,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>På Tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,10 +2192,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120223301</v>
+        <v>120222626</v>
       </c>
       <c r="B15" t="n">
-        <v>91228</v>
+        <v>90864</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,38 +2204,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>898</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566477</v>
+        <v>566559</v>
       </c>
       <c r="R15" t="n">
-        <v>7041729</v>
+        <v>7041473</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,7 +2267,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2258,7 +2277,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,10 +2304,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120222506</v>
+        <v>120223099</v>
       </c>
       <c r="B16" t="n">
-        <v>57463</v>
+        <v>91023</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,47 +2316,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566564</v>
+        <v>566497</v>
       </c>
       <c r="R16" t="n">
-        <v>7041444</v>
+        <v>7041610</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2369,7 +2379,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,7 +2389,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,10 +2416,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120223202</v>
+        <v>120223831</v>
       </c>
       <c r="B17" t="n">
-        <v>78526</v>
+        <v>90600</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,21 +2432,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2446,10 +2456,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566493</v>
+        <v>566397</v>
       </c>
       <c r="R17" t="n">
-        <v>7041714</v>
+        <v>7041615</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2481,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2491,7 +2501,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,22 +2516,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120223311</v>
+        <v>120222903</v>
       </c>
       <c r="B18" t="n">
-        <v>97907</v>
+        <v>82321</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2530,42 +2540,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566476</v>
+        <v>566505</v>
       </c>
       <c r="R18" t="n">
-        <v>7041727</v>
+        <v>7041563</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2597,7 +2603,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2607,7 +2613,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2634,10 +2640,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120222408</v>
+        <v>120222413</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2646,43 +2652,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566528</v>
+        <v>566568</v>
       </c>
       <c r="R19" t="n">
-        <v>7041423</v>
+        <v>7041467</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2714,7 +2715,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2724,12 +2725,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På Tall</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2744,22 +2740,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120222893</v>
+        <v>120223457</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2768,38 +2764,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566554</v>
+        <v>566452</v>
       </c>
       <c r="R20" t="n">
-        <v>7041587</v>
+        <v>7041743</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,12 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2861,22 +2856,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120222413</v>
+        <v>120223243</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>90923</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2885,38 +2880,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566568</v>
+        <v>566478</v>
       </c>
       <c r="R21" t="n">
-        <v>7041467</v>
+        <v>7041715</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2948,7 +2943,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2958,7 +2953,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,22 +2968,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120223457</v>
+        <v>120222471</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2997,42 +2992,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566452</v>
+        <v>566555</v>
       </c>
       <c r="R22" t="n">
-        <v>7041743</v>
+        <v>7041449</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3064,7 +3055,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3074,7 +3065,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3101,10 +3092,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120222471</v>
+        <v>120222972</v>
       </c>
       <c r="B23" t="n">
-        <v>90562</v>
+        <v>56532</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3113,41 +3104,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566555</v>
+        <v>566530</v>
       </c>
       <c r="R23" t="n">
-        <v>7041449</v>
+        <v>7041605</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3176,7 +3172,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3186,7 +3182,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3201,12 +3197,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3216,7 +3212,7 @@
         <v>120222649</v>
       </c>
       <c r="B24" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3335,10 +3331,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120222439</v>
+        <v>120223384</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>91023</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3347,38 +3343,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566548</v>
+        <v>566465</v>
       </c>
       <c r="R25" t="n">
-        <v>7041434</v>
+        <v>7041759</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3410,7 +3406,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3420,7 +3416,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3447,10 +3443,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120223243</v>
+        <v>120223311</v>
       </c>
       <c r="B26" t="n">
-        <v>90905</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3463,34 +3459,38 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566478</v>
+        <v>566476</v>
       </c>
       <c r="R26" t="n">
-        <v>7041715</v>
+        <v>7041727</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3559,10 +3559,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120222753</v>
+        <v>120222439</v>
       </c>
       <c r="B27" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3575,21 +3575,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566546</v>
+        <v>566548</v>
       </c>
       <c r="R27" t="n">
-        <v>7041554</v>
+        <v>7041434</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3671,10 +3671,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120222653</v>
+        <v>120222990</v>
       </c>
       <c r="B28" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3683,42 +3683,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566557</v>
+        <v>566475</v>
       </c>
       <c r="R28" t="n">
-        <v>7041495</v>
+        <v>7041565</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3750,7 +3746,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3760,7 +3756,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3787,10 +3783,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120223736</v>
+        <v>120222753</v>
       </c>
       <c r="B29" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3803,39 +3799,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566434</v>
+        <v>566546</v>
       </c>
       <c r="R29" t="n">
-        <v>7041848</v>
+        <v>7041554</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3867,7 +3858,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3877,7 +3868,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3904,10 +3895,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120223599</v>
+        <v>120222949</v>
       </c>
       <c r="B30" t="n">
-        <v>91228</v>
+        <v>56524</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3916,38 +3907,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>898</v>
+        <v>102612</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566435</v>
+        <v>566482</v>
       </c>
       <c r="R30" t="n">
-        <v>7041764</v>
+        <v>7041546</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4016,10 +4016,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120223345</v>
+        <v>120223301</v>
       </c>
       <c r="B31" t="n">
-        <v>79607</v>
+        <v>91246</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4028,25 +4028,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4056,10 +4056,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566473</v>
+        <v>566477</v>
       </c>
       <c r="R31" t="n">
-        <v>7041726</v>
+        <v>7041729</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 41505-2024 artfynd.xlsx
+++ b/artfynd/A 41505-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120222653</v>
+        <v>120223736</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,42 +916,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566557</v>
+        <v>566434</v>
       </c>
       <c r="R4" t="n">
-        <v>7041495</v>
+        <v>7041848</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120223736</v>
+        <v>120222506</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,39 +1037,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566434</v>
+        <v>566564</v>
       </c>
       <c r="R5" t="n">
-        <v>7041848</v>
+        <v>7041444</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120222506</v>
+        <v>120222653</v>
       </c>
       <c r="B6" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,35 +1154,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566564</v>
+        <v>566557</v>
       </c>
       <c r="R6" t="n">
-        <v>7041444</v>
+        <v>7041495</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1375,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120222579</v>
+        <v>120222384</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,31 +1387,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1420,10 +1419,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566558</v>
+        <v>566537</v>
       </c>
       <c r="R8" t="n">
-        <v>7041464</v>
+        <v>7041443</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1454,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,12 +1464,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,10 +1491,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120222384</v>
+        <v>120222579</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,30 +1503,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566537</v>
+        <v>566558</v>
       </c>
       <c r="R9" t="n">
-        <v>7041443</v>
+        <v>7041464</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,7 +1571,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1586,7 +1581,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2070,10 +2070,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120222408</v>
+        <v>120222626</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,39 +2086,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566528</v>
+        <v>566559</v>
       </c>
       <c r="R14" t="n">
-        <v>7041423</v>
+        <v>7041473</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2150,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2160,12 +2155,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På Tall</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,10 +2182,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120222626</v>
+        <v>120223099</v>
       </c>
       <c r="B15" t="n">
-        <v>90864</v>
+        <v>91023</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2204,38 +2194,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566559</v>
+        <v>566497</v>
       </c>
       <c r="R15" t="n">
-        <v>7041473</v>
+        <v>7041610</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2267,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2277,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2304,10 +2294,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120223099</v>
+        <v>120223831</v>
       </c>
       <c r="B16" t="n">
-        <v>91023</v>
+        <v>90600</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2316,25 +2306,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1209</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2344,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566497</v>
+        <v>566397</v>
       </c>
       <c r="R16" t="n">
-        <v>7041610</v>
+        <v>7041615</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2379,7 +2369,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2389,7 +2379,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,22 +2394,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120223831</v>
+        <v>120222408</v>
       </c>
       <c r="B17" t="n">
-        <v>90600</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2432,34 +2422,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566397</v>
+        <v>566528</v>
       </c>
       <c r="R17" t="n">
-        <v>7041615</v>
+        <v>7041423</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2491,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2501,7 +2496,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På Tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,12 +2516,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120223243</v>
+        <v>120222471</v>
       </c>
       <c r="B21" t="n">
-        <v>90923</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2880,38 +2880,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566478</v>
+        <v>566555</v>
       </c>
       <c r="R21" t="n">
-        <v>7041715</v>
+        <v>7041449</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2980,10 +2980,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120222471</v>
+        <v>120223243</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>90923</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2992,38 +2992,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566555</v>
+        <v>566478</v>
       </c>
       <c r="R22" t="n">
-        <v>7041449</v>
+        <v>7041715</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 41505-2024 artfynd.xlsx
+++ b/artfynd/A 41505-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120222893</v>
+        <v>120222653</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566554</v>
+        <v>566557</v>
       </c>
       <c r="R3" t="n">
-        <v>7041587</v>
+        <v>7041495</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,12 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,22 +891,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120223736</v>
+        <v>120223311</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,43 +915,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566434</v>
+        <v>566476</v>
       </c>
       <c r="R4" t="n">
-        <v>7041848</v>
+        <v>7041727</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120222506</v>
+        <v>120223243</v>
       </c>
       <c r="B5" t="n">
-        <v>57473</v>
+        <v>90923</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,47 +1031,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>2062</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566564</v>
+        <v>566478</v>
       </c>
       <c r="R5" t="n">
-        <v>7041444</v>
+        <v>7041715</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120222653</v>
+        <v>120222903</v>
       </c>
       <c r="B6" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,42 +1143,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566557</v>
+        <v>566505</v>
       </c>
       <c r="R6" t="n">
-        <v>7041495</v>
+        <v>7041563</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120222380</v>
+        <v>120223345</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1274,34 +1259,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566570</v>
+        <v>566473</v>
       </c>
       <c r="R7" t="n">
-        <v>7041464</v>
+        <v>7041726</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,12 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,22 +1343,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120222384</v>
+        <v>120222990</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,42 +1367,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566537</v>
+        <v>566475</v>
       </c>
       <c r="R8" t="n">
-        <v>7041443</v>
+        <v>7041565</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1454,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1464,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120222579</v>
+        <v>120222972</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>56532</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,46 +1479,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566558</v>
+        <v>566530</v>
       </c>
       <c r="R9" t="n">
-        <v>7041464</v>
+        <v>7041605</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1571,7 +1547,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1581,12 +1557,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,19 +1572,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120222763</v>
+        <v>120222893</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1653,10 +1624,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566538</v>
+        <v>566554</v>
       </c>
       <c r="R10" t="n">
-        <v>7041535</v>
+        <v>7041587</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1688,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1730,10 +1701,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120223345</v>
+        <v>120223301</v>
       </c>
       <c r="B11" t="n">
-        <v>79623</v>
+        <v>91246</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,25 +1713,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1770,10 +1741,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566473</v>
+        <v>566477</v>
       </c>
       <c r="R11" t="n">
-        <v>7041726</v>
+        <v>7041729</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1805,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,7 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,10 +1813,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120223599</v>
+        <v>120222579</v>
       </c>
       <c r="B12" t="n">
-        <v>91246</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,38 +1825,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566435</v>
+        <v>566558</v>
       </c>
       <c r="R12" t="n">
-        <v>7041764</v>
+        <v>7041464</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1917,7 +1893,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1927,7 +1903,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120223955</v>
+        <v>120222380</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1966,42 +1947,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566345</v>
+        <v>566570</v>
       </c>
       <c r="R13" t="n">
-        <v>7041782</v>
+        <v>7041464</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2043,7 +2020,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2058,22 +2040,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120222626</v>
+        <v>120222763</v>
       </c>
       <c r="B14" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,21 +2068,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2110,10 +2092,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566559</v>
+        <v>566538</v>
       </c>
       <c r="R14" t="n">
-        <v>7041473</v>
+        <v>7041535</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2145,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2137,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,22 +2157,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120223099</v>
+        <v>120222439</v>
       </c>
       <c r="B15" t="n">
-        <v>91023</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,38 +2181,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566497</v>
+        <v>566548</v>
       </c>
       <c r="R15" t="n">
-        <v>7041610</v>
+        <v>7041434</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2257,7 +2244,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2254,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,10 +2281,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120223831</v>
+        <v>120222471</v>
       </c>
       <c r="B16" t="n">
-        <v>90600</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2310,34 +2297,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566397</v>
+        <v>566555</v>
       </c>
       <c r="R16" t="n">
-        <v>7041615</v>
+        <v>7041449</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2369,7 +2356,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,7 +2366,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,19 +2381,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120222408</v>
+        <v>120222649</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2451,10 +2438,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566528</v>
+        <v>566556</v>
       </c>
       <c r="R17" t="n">
-        <v>7041423</v>
+        <v>7041534</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2486,7 +2473,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2496,12 +2483,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,22 +2503,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120222903</v>
+        <v>120222408</v>
       </c>
       <c r="B18" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,34 +2531,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566505</v>
+        <v>566528</v>
       </c>
       <c r="R18" t="n">
-        <v>7041563</v>
+        <v>7041423</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2603,7 +2595,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,7 +2605,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På Tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2640,10 +2637,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120222413</v>
+        <v>120223831</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>90600</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2652,38 +2649,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566568</v>
+        <v>566397</v>
       </c>
       <c r="R19" t="n">
-        <v>7041467</v>
+        <v>7041615</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2715,7 +2712,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2725,7 +2722,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2752,10 +2749,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120223457</v>
+        <v>120222506</v>
       </c>
       <c r="B20" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2764,42 +2761,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566452</v>
+        <v>566564</v>
       </c>
       <c r="R20" t="n">
-        <v>7041743</v>
+        <v>7041444</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2833,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,7 +2843,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2868,10 +2870,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120222471</v>
+        <v>120222949</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>56524</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2884,34 +2886,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566555</v>
+        <v>566482</v>
       </c>
       <c r="R21" t="n">
-        <v>7041449</v>
+        <v>7041546</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2943,7 +2954,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2953,7 +2964,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2980,10 +2991,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120223243</v>
+        <v>120222384</v>
       </c>
       <c r="B22" t="n">
-        <v>90923</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2996,34 +3007,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566478</v>
+        <v>566537</v>
       </c>
       <c r="R22" t="n">
-        <v>7041715</v>
+        <v>7041443</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3055,7 +3070,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3065,7 +3080,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3092,10 +3107,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120222972</v>
+        <v>120223955</v>
       </c>
       <c r="B23" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3104,46 +3119,45 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566530</v>
+        <v>566345</v>
       </c>
       <c r="R23" t="n">
-        <v>7041605</v>
+        <v>7041782</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3172,7 +3186,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3182,7 +3196,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3197,22 +3211,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120222649</v>
+        <v>120223099</v>
       </c>
       <c r="B24" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3221,43 +3235,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566556</v>
+        <v>566497</v>
       </c>
       <c r="R24" t="n">
-        <v>7041534</v>
+        <v>7041610</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3289,7 +3298,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3299,12 +3308,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3319,22 +3323,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120223384</v>
+        <v>120222626</v>
       </c>
       <c r="B25" t="n">
-        <v>91023</v>
+        <v>90864</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3343,38 +3347,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566465</v>
+        <v>566559</v>
       </c>
       <c r="R25" t="n">
-        <v>7041759</v>
+        <v>7041473</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3406,7 +3410,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3416,7 +3420,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3443,10 +3447,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120223311</v>
+        <v>120223599</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>91246</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3459,38 +3463,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>898</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Fr.) Vesterholt</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566476</v>
+        <v>566435</v>
       </c>
       <c r="R26" t="n">
-        <v>7041727</v>
+        <v>7041764</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3559,10 +3559,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120222439</v>
+        <v>120223457</v>
       </c>
       <c r="B27" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3571,38 +3571,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566548</v>
+        <v>566452</v>
       </c>
       <c r="R27" t="n">
-        <v>7041434</v>
+        <v>7041743</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3634,7 +3638,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3644,7 +3648,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3671,10 +3675,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120222990</v>
+        <v>120222413</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3683,38 +3687,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566475</v>
+        <v>566568</v>
       </c>
       <c r="R28" t="n">
-        <v>7041565</v>
+        <v>7041467</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3746,7 +3750,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3756,7 +3760,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3771,22 +3775,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120222753</v>
+        <v>120223384</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>91023</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3795,38 +3799,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566546</v>
+        <v>566465</v>
       </c>
       <c r="R29" t="n">
-        <v>7041554</v>
+        <v>7041759</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3858,7 +3862,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3868,7 +3872,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3895,10 +3899,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120222949</v>
+        <v>120222753</v>
       </c>
       <c r="B30" t="n">
-        <v>56524</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3911,43 +3915,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566482</v>
+        <v>566546</v>
       </c>
       <c r="R30" t="n">
-        <v>7041546</v>
+        <v>7041554</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3979,7 +3974,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3989,7 +3984,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4016,10 +4011,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120223301</v>
+        <v>120223736</v>
       </c>
       <c r="B31" t="n">
-        <v>91246</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4028,38 +4023,43 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566477</v>
+        <v>566434</v>
       </c>
       <c r="R31" t="n">
-        <v>7041729</v>
+        <v>7041848</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 41505-2024 artfynd.xlsx
+++ b/artfynd/A 41505-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120223202</v>
+        <v>120222653</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566493</v>
+        <v>566557</v>
       </c>
       <c r="R2" t="n">
-        <v>7041714</v>
+        <v>7041495</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120222653</v>
+        <v>120223311</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -822,19 +826,19 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566557</v>
+        <v>566476</v>
       </c>
       <c r="R3" t="n">
-        <v>7041495</v>
+        <v>7041727</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120223311</v>
+        <v>120223202</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,42 +919,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566476</v>
+        <v>566493</v>
       </c>
       <c r="R4" t="n">
-        <v>7041727</v>
+        <v>7041714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1467,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120222972</v>
+        <v>120222893</v>
       </c>
       <c r="B9" t="n">
-        <v>56532</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,46 +1479,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566530</v>
+        <v>566554</v>
       </c>
       <c r="R9" t="n">
-        <v>7041605</v>
+        <v>7041587</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1547,7 +1542,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1557,7 +1552,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120222893</v>
+        <v>120223301</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>91246</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1596,38 +1596,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566554</v>
+        <v>566477</v>
       </c>
       <c r="R10" t="n">
-        <v>7041587</v>
+        <v>7041729</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,12 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,22 +1684,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120223301</v>
+        <v>120222972</v>
       </c>
       <c r="B11" t="n">
-        <v>91246</v>
+        <v>56532</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,41 +1708,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>898</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566477</v>
+        <v>566530</v>
       </c>
       <c r="R11" t="n">
-        <v>7041729</v>
+        <v>7041605</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,12 +1801,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 41505-2024 artfynd.xlsx
+++ b/artfynd/A 41505-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120222653</v>
+        <v>120223099</v>
       </c>
       <c r="B2" t="n">
-        <v>97930</v>
+        <v>91023</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566557</v>
+        <v>566497</v>
       </c>
       <c r="R2" t="n">
-        <v>7041495</v>
+        <v>7041610</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120223311</v>
+        <v>120222653</v>
       </c>
       <c r="B3" t="n">
         <v>97930</v>
@@ -826,19 +822,19 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566476</v>
+        <v>566557</v>
       </c>
       <c r="R3" t="n">
-        <v>7041727</v>
+        <v>7041495</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120223202</v>
+        <v>120222649</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,34 +919,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566493</v>
+        <v>566556</v>
       </c>
       <c r="R4" t="n">
-        <v>7041714</v>
+        <v>7041534</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120223243</v>
+        <v>120223831</v>
       </c>
       <c r="B5" t="n">
-        <v>90923</v>
+        <v>90600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,25 +1037,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2062</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566478</v>
+        <v>566397</v>
       </c>
       <c r="R5" t="n">
-        <v>7041715</v>
+        <v>7041615</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120222903</v>
+        <v>120223243</v>
       </c>
       <c r="B6" t="n">
-        <v>82321</v>
+        <v>90923</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,25 +1149,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>2062</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566505</v>
+        <v>566478</v>
       </c>
       <c r="R6" t="n">
-        <v>7041563</v>
+        <v>7041715</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120223345</v>
+        <v>120222384</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,38 +1261,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566473</v>
+        <v>566537</v>
       </c>
       <c r="R7" t="n">
-        <v>7041726</v>
+        <v>7041443</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120222990</v>
+        <v>120223599</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>91246</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1367,38 +1377,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>898</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566475</v>
+        <v>566435</v>
       </c>
       <c r="R8" t="n">
-        <v>7041565</v>
+        <v>7041764</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,7 +1440,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,7 +1450,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,10 +1477,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120222893</v>
+        <v>120223955</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,38 +1489,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566554</v>
+        <v>566345</v>
       </c>
       <c r="R9" t="n">
-        <v>7041587</v>
+        <v>7041782</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1552,12 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,22 +1581,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120223301</v>
+        <v>120223457</v>
       </c>
       <c r="B10" t="n">
-        <v>91246</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,34 +1609,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566477</v>
+        <v>566452</v>
       </c>
       <c r="R10" t="n">
-        <v>7041729</v>
+        <v>7041743</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1659,7 +1672,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1682,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120222972</v>
+        <v>120223384</v>
       </c>
       <c r="B11" t="n">
-        <v>56532</v>
+        <v>91023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,46 +1721,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566530</v>
+        <v>566465</v>
       </c>
       <c r="R11" t="n">
-        <v>7041605</v>
+        <v>7041759</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,22 +1809,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120222579</v>
+        <v>120223301</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>91246</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,43 +1833,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566558</v>
+        <v>566477</v>
       </c>
       <c r="R12" t="n">
-        <v>7041464</v>
+        <v>7041729</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1893,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1903,12 +1906,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1935,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120222380</v>
+        <v>120222471</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,21 +1949,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1975,10 +1973,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566570</v>
+        <v>566555</v>
       </c>
       <c r="R13" t="n">
-        <v>7041464</v>
+        <v>7041449</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2010,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,12 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2040,19 +2033,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120222763</v>
+        <v>120222579</v>
       </c>
       <c r="B14" t="n">
         <v>57320</v>
@@ -2086,16 +2079,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566538</v>
+        <v>566558</v>
       </c>
       <c r="R14" t="n">
-        <v>7041535</v>
+        <v>7041464</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,7 +2125,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2137,12 +2135,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,22 +2155,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120222439</v>
+        <v>120222949</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>56524</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,34 +2183,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566548</v>
+        <v>566482</v>
       </c>
       <c r="R15" t="n">
-        <v>7041434</v>
+        <v>7041546</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2244,7 +2251,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2254,7 +2261,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2281,10 +2288,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120222471</v>
+        <v>120222413</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>91858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2293,25 +2300,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2321,10 +2328,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566555</v>
+        <v>566568</v>
       </c>
       <c r="R16" t="n">
-        <v>7041449</v>
+        <v>7041467</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2356,7 +2363,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2366,7 +2373,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2381,22 +2388,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120222649</v>
+        <v>120222439</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2409,39 +2416,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566556</v>
+        <v>566548</v>
       </c>
       <c r="R17" t="n">
-        <v>7041534</v>
+        <v>7041434</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2473,7 +2475,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2483,12 +2485,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2503,22 +2500,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120222408</v>
+        <v>120223202</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,39 +2528,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566528</v>
+        <v>566493</v>
       </c>
       <c r="R18" t="n">
-        <v>7041423</v>
+        <v>7041714</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2595,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2605,12 +2597,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På Tall</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2637,10 +2624,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120223831</v>
+        <v>120223345</v>
       </c>
       <c r="B19" t="n">
-        <v>90600</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2653,21 +2640,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2677,10 +2664,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566397</v>
+        <v>566473</v>
       </c>
       <c r="R19" t="n">
-        <v>7041615</v>
+        <v>7041726</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2712,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2722,7 +2709,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2737,22 +2724,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120222506</v>
+        <v>120222408</v>
       </c>
       <c r="B20" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2765,31 +2752,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2798,10 +2781,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566564</v>
+        <v>566528</v>
       </c>
       <c r="R20" t="n">
-        <v>7041444</v>
+        <v>7041423</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2833,7 +2816,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2843,7 +2826,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,10 +2858,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120222949</v>
+        <v>120222972</v>
       </c>
       <c r="B21" t="n">
-        <v>56524</v>
+        <v>56532</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2882,35 +2870,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2919,13 +2903,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566482</v>
+        <v>566530</v>
       </c>
       <c r="R21" t="n">
-        <v>7041546</v>
+        <v>7041605</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2954,7 +2938,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2964,7 +2948,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2979,22 +2963,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120222384</v>
+        <v>120222626</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3003,42 +2987,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566537</v>
+        <v>566559</v>
       </c>
       <c r="R22" t="n">
-        <v>7041443</v>
+        <v>7041473</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3070,7 +3050,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3080,7 +3060,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3107,10 +3087,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120223955</v>
+        <v>120222903</v>
       </c>
       <c r="B23" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3119,42 +3099,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566345</v>
+        <v>566505</v>
       </c>
       <c r="R23" t="n">
-        <v>7041782</v>
+        <v>7041563</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3186,7 +3162,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3196,7 +3172,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3223,10 +3199,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120223099</v>
+        <v>120222753</v>
       </c>
       <c r="B24" t="n">
-        <v>91023</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3235,38 +3211,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566497</v>
+        <v>566546</v>
       </c>
       <c r="R24" t="n">
-        <v>7041610</v>
+        <v>7041554</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3298,7 +3274,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3308,7 +3284,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3335,10 +3311,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120222626</v>
+        <v>120222990</v>
       </c>
       <c r="B25" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3351,34 +3327,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566559</v>
+        <v>566475</v>
       </c>
       <c r="R25" t="n">
-        <v>7041473</v>
+        <v>7041565</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3410,7 +3386,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3420,7 +3396,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3447,10 +3423,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120223599</v>
+        <v>120222380</v>
       </c>
       <c r="B26" t="n">
-        <v>91246</v>
+        <v>57320</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3459,38 +3435,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566435</v>
+        <v>566570</v>
       </c>
       <c r="R26" t="n">
-        <v>7041764</v>
+        <v>7041464</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3522,7 +3498,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3532,7 +3508,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3547,22 +3528,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120223457</v>
+        <v>120222763</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3571,42 +3552,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566452</v>
+        <v>566538</v>
       </c>
       <c r="R27" t="n">
-        <v>7041743</v>
+        <v>7041535</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3638,7 +3615,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3648,7 +3625,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3663,22 +3645,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120222413</v>
+        <v>120222506</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3687,38 +3669,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566568</v>
+        <v>566564</v>
       </c>
       <c r="R28" t="n">
-        <v>7041467</v>
+        <v>7041444</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3750,7 +3741,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3760,7 +3751,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3775,22 +3766,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120223384</v>
+        <v>120223311</v>
       </c>
       <c r="B29" t="n">
-        <v>91023</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3803,34 +3794,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566465</v>
+        <v>566476</v>
       </c>
       <c r="R29" t="n">
-        <v>7041759</v>
+        <v>7041727</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3862,7 +3857,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3872,7 +3867,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3899,10 +3894,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120222753</v>
+        <v>120222893</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3915,21 +3910,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3939,10 +3934,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566546</v>
+        <v>566554</v>
       </c>
       <c r="R30" t="n">
-        <v>7041554</v>
+        <v>7041587</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3974,7 +3969,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3984,7 +3979,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3999,12 +3999,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 41505-2024 artfynd.xlsx
+++ b/artfynd/A 41505-2024 artfynd.xlsx
@@ -1821,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120223301</v>
+        <v>120222579</v>
       </c>
       <c r="B12" t="n">
-        <v>91246</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,38 +1833,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566477</v>
+        <v>566558</v>
       </c>
       <c r="R12" t="n">
-        <v>7041729</v>
+        <v>7041464</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1901,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,7 +1911,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120222471</v>
+        <v>120223301</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>91246</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,38 +1955,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566555</v>
+        <v>566477</v>
       </c>
       <c r="R13" t="n">
-        <v>7041449</v>
+        <v>7041729</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2008,7 +2018,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +2028,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120222579</v>
+        <v>120222471</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2061,39 +2071,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566558</v>
+        <v>566555</v>
       </c>
       <c r="R14" t="n">
-        <v>7041464</v>
+        <v>7041449</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2125,7 +2130,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2135,12 +2140,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -3778,10 +3778,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120223311</v>
+        <v>120222893</v>
       </c>
       <c r="B29" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3790,42 +3790,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566476</v>
+        <v>566554</v>
       </c>
       <c r="R29" t="n">
-        <v>7041727</v>
+        <v>7041587</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3857,7 +3853,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3867,7 +3863,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3882,19 +3883,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120222893</v>
+        <v>120223736</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3928,16 +3929,21 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566554</v>
+        <v>566434</v>
       </c>
       <c r="R30" t="n">
-        <v>7041587</v>
+        <v>7041848</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3969,7 +3975,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3979,12 +3985,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3999,22 +4000,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120223736</v>
+        <v>120223311</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4023,43 +4024,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566434</v>
+        <v>566476</v>
       </c>
       <c r="R31" t="n">
-        <v>7041848</v>
+        <v>7041727</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 41505-2024 artfynd.xlsx
+++ b/artfynd/A 41505-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120223099</v>
+        <v>120222903</v>
       </c>
       <c r="B2" t="n">
-        <v>91023</v>
+        <v>82321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566497</v>
+        <v>566505</v>
       </c>
       <c r="R2" t="n">
-        <v>7041610</v>
+        <v>7041563</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120222653</v>
+        <v>120223736</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +799,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566557</v>
+        <v>566434</v>
       </c>
       <c r="R3" t="n">
-        <v>7041495</v>
+        <v>7041848</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1025,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120223831</v>
+        <v>120223202</v>
       </c>
       <c r="B5" t="n">
-        <v>90600</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,21 +1042,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566397</v>
+        <v>566493</v>
       </c>
       <c r="R5" t="n">
-        <v>7041615</v>
+        <v>7041714</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120223243</v>
+        <v>120222439</v>
       </c>
       <c r="B6" t="n">
-        <v>90923</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,38 +1150,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566478</v>
+        <v>566548</v>
       </c>
       <c r="R6" t="n">
-        <v>7041715</v>
+        <v>7041434</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120222384</v>
+        <v>120223243</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>90923</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,38 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566537</v>
+        <v>566478</v>
       </c>
       <c r="R7" t="n">
-        <v>7041443</v>
+        <v>7041715</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,7 +1362,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120223599</v>
+        <v>120223301</v>
       </c>
       <c r="B8" t="n">
         <v>91246</v>
@@ -1401,14 +1398,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566435</v>
+        <v>566477</v>
       </c>
       <c r="R8" t="n">
-        <v>7041764</v>
+        <v>7041729</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120223955</v>
+        <v>120222753</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,42 +1486,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566345</v>
+        <v>566546</v>
       </c>
       <c r="R9" t="n">
-        <v>7041782</v>
+        <v>7041554</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120223457</v>
+        <v>120222949</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>56524</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,30 +1598,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1637,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566452</v>
+        <v>566482</v>
       </c>
       <c r="R10" t="n">
-        <v>7041743</v>
+        <v>7041546</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,7 +1680,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120223384</v>
+        <v>120222408</v>
       </c>
       <c r="B11" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,38 +1719,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566465</v>
+        <v>566528</v>
       </c>
       <c r="R11" t="n">
-        <v>7041759</v>
+        <v>7041423</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1784,7 +1787,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1797,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På Tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,10 +1829,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120222579</v>
+        <v>120223831</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>90600</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,39 +1845,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566558</v>
+        <v>566397</v>
       </c>
       <c r="R12" t="n">
-        <v>7041464</v>
+        <v>7041615</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,12 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,22 +1929,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120223301</v>
+        <v>120223955</v>
       </c>
       <c r="B13" t="n">
-        <v>91246</v>
+        <v>97930</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,34 +1957,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566477</v>
+        <v>566345</v>
       </c>
       <c r="R13" t="n">
-        <v>7041729</v>
+        <v>7041782</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,7 +2020,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,7 +2030,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,10 +2057,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120222471</v>
+        <v>120222506</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,34 +2073,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566555</v>
+        <v>566564</v>
       </c>
       <c r="R14" t="n">
-        <v>7041449</v>
+        <v>7041444</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,7 +2141,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2140,7 +2151,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,10 +2178,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120222949</v>
+        <v>120222893</v>
       </c>
       <c r="B15" t="n">
-        <v>56524</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2183,16 +2194,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2200,26 +2211,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566482</v>
+        <v>566554</v>
       </c>
       <c r="R15" t="n">
-        <v>7041546</v>
+        <v>7041587</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2251,7 +2253,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2261,7 +2263,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2276,12 +2283,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2400,10 +2407,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120222439</v>
+        <v>120222579</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2416,34 +2423,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566548</v>
+        <v>566558</v>
       </c>
       <c r="R17" t="n">
-        <v>7041434</v>
+        <v>7041464</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2475,7 +2487,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2485,7 +2497,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,10 +2529,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120223202</v>
+        <v>120223457</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2524,38 +2541,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566493</v>
+        <v>566452</v>
       </c>
       <c r="R18" t="n">
-        <v>7041714</v>
+        <v>7041743</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,7 +2608,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,7 +2618,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2624,10 +2645,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120223345</v>
+        <v>120223599</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>91246</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2636,38 +2657,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566473</v>
+        <v>566435</v>
       </c>
       <c r="R19" t="n">
-        <v>7041726</v>
+        <v>7041764</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,7 +2720,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,7 +2730,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,10 +2757,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120222408</v>
+        <v>120222990</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2752,39 +2773,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566528</v>
+        <v>566475</v>
       </c>
       <c r="R20" t="n">
-        <v>7041423</v>
+        <v>7041565</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2816,7 +2832,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2826,12 +2842,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På Tall</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2858,10 +2869,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120222972</v>
+        <v>120223311</v>
       </c>
       <c r="B21" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2870,31 +2881,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>stationär</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2903,13 +2913,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566530</v>
+        <v>566476</v>
       </c>
       <c r="R21" t="n">
-        <v>7041605</v>
+        <v>7041727</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2938,7 +2948,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2948,7 +2958,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,22 +2973,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120222626</v>
+        <v>120222471</v>
       </c>
       <c r="B22" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2991,21 +3001,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3015,10 +3025,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566559</v>
+        <v>566555</v>
       </c>
       <c r="R22" t="n">
-        <v>7041473</v>
+        <v>7041449</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3050,7 +3060,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3060,7 +3070,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3087,10 +3097,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120222903</v>
+        <v>120223345</v>
       </c>
       <c r="B23" t="n">
-        <v>82321</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3103,21 +3113,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3127,10 +3137,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566505</v>
+        <v>566473</v>
       </c>
       <c r="R23" t="n">
-        <v>7041563</v>
+        <v>7041726</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3162,7 +3172,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3172,7 +3182,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3199,10 +3209,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120222753</v>
+        <v>120223099</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>91023</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3211,38 +3221,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566546</v>
+        <v>566497</v>
       </c>
       <c r="R24" t="n">
-        <v>7041554</v>
+        <v>7041610</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3274,7 +3284,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3284,7 +3294,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3311,10 +3321,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120222990</v>
+        <v>120223384</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>91023</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3323,25 +3333,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3351,10 +3361,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566475</v>
+        <v>566465</v>
       </c>
       <c r="R25" t="n">
-        <v>7041565</v>
+        <v>7041759</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3386,7 +3396,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3396,7 +3406,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3423,10 +3433,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120222380</v>
+        <v>120222972</v>
       </c>
       <c r="B26" t="n">
-        <v>57320</v>
+        <v>56532</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3435,41 +3445,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566570</v>
+        <v>566530</v>
       </c>
       <c r="R26" t="n">
-        <v>7041464</v>
+        <v>7041605</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3498,7 +3513,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3508,12 +3523,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3540,10 +3550,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120222763</v>
+        <v>120222384</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3552,38 +3562,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566538</v>
+        <v>566537</v>
       </c>
       <c r="R27" t="n">
-        <v>7041535</v>
+        <v>7041443</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3615,7 +3629,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3625,12 +3639,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3645,22 +3654,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120222506</v>
+        <v>120222653</v>
       </c>
       <c r="B28" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3669,35 +3678,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3706,10 +3710,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566564</v>
+        <v>566557</v>
       </c>
       <c r="R28" t="n">
-        <v>7041444</v>
+        <v>7041495</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3741,7 +3745,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3751,7 +3755,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3778,7 +3782,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120222893</v>
+        <v>120222380</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3818,10 +3822,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566554</v>
+        <v>566570</v>
       </c>
       <c r="R29" t="n">
-        <v>7041587</v>
+        <v>7041464</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3853,7 +3857,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3863,7 +3867,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3895,7 +3899,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120223736</v>
+        <v>120222763</v>
       </c>
       <c r="B30" t="n">
         <v>57320</v>
@@ -3929,21 +3933,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566434</v>
+        <v>566538</v>
       </c>
       <c r="R30" t="n">
-        <v>7041848</v>
+        <v>7041535</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3975,7 +3974,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3985,7 +3984,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4000,22 +4004,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120223311</v>
+        <v>120222626</v>
       </c>
       <c r="B31" t="n">
-        <v>97930</v>
+        <v>90864</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4024,42 +4028,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566476</v>
+        <v>566559</v>
       </c>
       <c r="R31" t="n">
-        <v>7041727</v>
+        <v>7041473</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 41505-2024 artfynd.xlsx
+++ b/artfynd/A 41505-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120222903</v>
+        <v>120222626</v>
       </c>
       <c r="B2" t="n">
-        <v>82321</v>
+        <v>90864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566505</v>
+        <v>566559</v>
       </c>
       <c r="R2" t="n">
-        <v>7041563</v>
+        <v>7041473</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120223736</v>
+        <v>120223955</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,31 +799,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566434</v>
+        <v>566345</v>
       </c>
       <c r="R3" t="n">
-        <v>7041848</v>
+        <v>7041782</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120222649</v>
+        <v>120222972</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>56532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,46 +915,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566556</v>
+        <v>566530</v>
       </c>
       <c r="R4" t="n">
-        <v>7041534</v>
+        <v>7041605</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120223202</v>
+        <v>120222893</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,34 +1036,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566493</v>
+        <v>566554</v>
       </c>
       <c r="R5" t="n">
-        <v>7041714</v>
+        <v>7041587</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1105,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120222439</v>
+        <v>120223736</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1153,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566548</v>
+        <v>566434</v>
       </c>
       <c r="R6" t="n">
-        <v>7041434</v>
+        <v>7041848</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120223243</v>
+        <v>120223457</v>
       </c>
       <c r="B7" t="n">
-        <v>90923</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,34 +1270,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2062</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566478</v>
+        <v>566452</v>
       </c>
       <c r="R7" t="n">
-        <v>7041715</v>
+        <v>7041743</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1343,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120223301</v>
+        <v>120223345</v>
       </c>
       <c r="B8" t="n">
-        <v>91246</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1374,25 +1382,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566477</v>
+        <v>566473</v>
       </c>
       <c r="R8" t="n">
-        <v>7041729</v>
+        <v>7041726</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1437,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120222753</v>
+        <v>120222649</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,34 +1498,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566546</v>
+        <v>566556</v>
       </c>
       <c r="R9" t="n">
-        <v>7041554</v>
+        <v>7041534</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1572,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,22 +1592,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120222949</v>
+        <v>120222413</v>
       </c>
       <c r="B10" t="n">
-        <v>56524</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,47 +1616,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566482</v>
+        <v>566568</v>
       </c>
       <c r="R10" t="n">
-        <v>7041546</v>
+        <v>7041467</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1689,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,22 +1704,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120222408</v>
+        <v>120223384</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,43 +1728,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566528</v>
+        <v>566465</v>
       </c>
       <c r="R11" t="n">
-        <v>7041423</v>
+        <v>7041759</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1787,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,12 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På Tall</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120223831</v>
+        <v>120222380</v>
       </c>
       <c r="B12" t="n">
-        <v>90600</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,34 +1844,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566397</v>
+        <v>566570</v>
       </c>
       <c r="R12" t="n">
-        <v>7041615</v>
+        <v>7041464</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1913,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,7 +1945,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120223955</v>
+        <v>120223311</v>
       </c>
       <c r="B13" t="n">
         <v>97930</v>
@@ -1976,19 +1980,19 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566345</v>
+        <v>566476</v>
       </c>
       <c r="R13" t="n">
-        <v>7041782</v>
+        <v>7041727</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2020,7 +2024,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2030,7 +2034,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2057,10 +2061,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120222506</v>
+        <v>120223099</v>
       </c>
       <c r="B14" t="n">
-        <v>57473</v>
+        <v>91023</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,47 +2073,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566564</v>
+        <v>566497</v>
       </c>
       <c r="R14" t="n">
-        <v>7041444</v>
+        <v>7041610</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2141,7 +2136,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2151,7 +2146,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,10 +2173,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120222893</v>
+        <v>120223831</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>90600</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,34 +2189,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566554</v>
+        <v>566397</v>
       </c>
       <c r="R15" t="n">
-        <v>7041587</v>
+        <v>7041615</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2253,7 +2248,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2263,12 +2258,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2295,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120222413</v>
+        <v>120222949</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>56524</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,38 +2297,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566568</v>
+        <v>566482</v>
       </c>
       <c r="R16" t="n">
-        <v>7041467</v>
+        <v>7041546</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2370,7 +2369,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2380,7 +2379,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,22 +2394,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120222579</v>
+        <v>120223301</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>91246</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2419,43 +2418,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566558</v>
+        <v>566477</v>
       </c>
       <c r="R17" t="n">
-        <v>7041464</v>
+        <v>7041729</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2487,7 +2481,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2497,12 +2491,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2529,10 +2518,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120223457</v>
+        <v>120222439</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2541,42 +2530,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566452</v>
+        <v>566548</v>
       </c>
       <c r="R18" t="n">
-        <v>7041743</v>
+        <v>7041434</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2608,7 +2593,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2618,7 +2603,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2645,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120223599</v>
+        <v>120223202</v>
       </c>
       <c r="B19" t="n">
-        <v>91246</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2657,38 +2642,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566435</v>
+        <v>566493</v>
       </c>
       <c r="R19" t="n">
-        <v>7041764</v>
+        <v>7041714</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2720,7 +2705,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2730,7 +2715,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2757,10 +2742,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120222990</v>
+        <v>120222408</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2773,34 +2758,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566475</v>
+        <v>566528</v>
       </c>
       <c r="R20" t="n">
-        <v>7041565</v>
+        <v>7041423</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2832,7 +2822,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2842,7 +2832,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På Tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2869,10 +2864,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120223311</v>
+        <v>120222506</v>
       </c>
       <c r="B21" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2881,42 +2876,47 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566476</v>
+        <v>566564</v>
       </c>
       <c r="R21" t="n">
-        <v>7041727</v>
+        <v>7041444</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2985,10 +2985,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120222471</v>
+        <v>120222384</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2997,38 +2997,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566555</v>
+        <v>566537</v>
       </c>
       <c r="R22" t="n">
-        <v>7041449</v>
+        <v>7041443</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3060,7 +3064,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3070,7 +3074,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3097,10 +3101,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120223345</v>
+        <v>120223599</v>
       </c>
       <c r="B23" t="n">
-        <v>79623</v>
+        <v>91246</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3109,38 +3113,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566473</v>
+        <v>566435</v>
       </c>
       <c r="R23" t="n">
-        <v>7041726</v>
+        <v>7041764</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3172,7 +3176,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3182,7 +3186,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,10 +3213,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120223099</v>
+        <v>120222653</v>
       </c>
       <c r="B24" t="n">
-        <v>91023</v>
+        <v>97930</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3225,34 +3229,38 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566497</v>
+        <v>566557</v>
       </c>
       <c r="R24" t="n">
-        <v>7041610</v>
+        <v>7041495</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3284,7 +3292,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3294,7 +3302,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3321,10 +3329,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120223384</v>
+        <v>120222763</v>
       </c>
       <c r="B25" t="n">
-        <v>91023</v>
+        <v>57320</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3333,38 +3341,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566465</v>
+        <v>566538</v>
       </c>
       <c r="R25" t="n">
-        <v>7041759</v>
+        <v>7041535</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3396,7 +3404,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3406,7 +3414,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3421,22 +3434,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120222972</v>
+        <v>120222903</v>
       </c>
       <c r="B26" t="n">
-        <v>56532</v>
+        <v>82321</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3445,46 +3458,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566530</v>
+        <v>566505</v>
       </c>
       <c r="R26" t="n">
-        <v>7041605</v>
+        <v>7041563</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3513,7 +3521,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3523,7 +3531,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3538,22 +3546,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120222384</v>
+        <v>120222990</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3562,42 +3570,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566537</v>
+        <v>566475</v>
       </c>
       <c r="R27" t="n">
-        <v>7041443</v>
+        <v>7041565</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3629,7 +3633,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3639,7 +3643,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3666,10 +3670,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120222653</v>
+        <v>120222753</v>
       </c>
       <c r="B28" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3678,42 +3682,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566557</v>
+        <v>566546</v>
       </c>
       <c r="R28" t="n">
-        <v>7041495</v>
+        <v>7041554</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3782,7 +3782,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120222380</v>
+        <v>120222579</v>
       </c>
       <c r="B29" t="n">
         <v>57320</v>
@@ -3816,13 +3816,18 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566570</v>
+        <v>566558</v>
       </c>
       <c r="R29" t="n">
         <v>7041464</v>
@@ -3857,7 +3862,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3867,12 +3872,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3887,22 +3892,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120222763</v>
+        <v>120223243</v>
       </c>
       <c r="B30" t="n">
-        <v>57320</v>
+        <v>90923</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3911,38 +3916,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566538</v>
+        <v>566478</v>
       </c>
       <c r="R30" t="n">
-        <v>7041535</v>
+        <v>7041715</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3974,7 +3979,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3984,12 +3989,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4004,22 +4004,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120222626</v>
+        <v>120222471</v>
       </c>
       <c r="B31" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4032,21 +4032,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4056,10 +4056,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566559</v>
+        <v>566555</v>
       </c>
       <c r="R31" t="n">
-        <v>7041473</v>
+        <v>7041449</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 41505-2024 artfynd.xlsx
+++ b/artfynd/A 41505-2024 artfynd.xlsx
@@ -1137,10 +1137,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120223736</v>
+        <v>120223345</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,39 +1153,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566434</v>
+        <v>566473</v>
       </c>
       <c r="R6" t="n">
-        <v>7041848</v>
+        <v>7041726</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1370,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120223345</v>
+        <v>120223736</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,34 +1381,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566473</v>
+        <v>566434</v>
       </c>
       <c r="R8" t="n">
-        <v>7041726</v>
+        <v>7041848</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1604,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120222413</v>
+        <v>120223384</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>91023</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,38 +1616,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566568</v>
+        <v>566465</v>
       </c>
       <c r="R10" t="n">
-        <v>7041467</v>
+        <v>7041759</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,22 +1704,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120223384</v>
+        <v>120222413</v>
       </c>
       <c r="B11" t="n">
-        <v>91023</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,38 +1728,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566465</v>
+        <v>566568</v>
       </c>
       <c r="R11" t="n">
-        <v>7041759</v>
+        <v>7041467</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,12 +1816,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2630,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120223202</v>
+        <v>120222408</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2646,34 +2646,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566493</v>
+        <v>566528</v>
       </c>
       <c r="R19" t="n">
-        <v>7041714</v>
+        <v>7041423</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2705,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2715,7 +2720,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På Tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2742,10 +2752,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120222408</v>
+        <v>120222506</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2758,27 +2768,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2787,10 +2801,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566528</v>
+        <v>566564</v>
       </c>
       <c r="R20" t="n">
-        <v>7041423</v>
+        <v>7041444</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2822,7 +2836,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2832,12 +2846,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På Tall</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2864,10 +2873,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120222506</v>
+        <v>120223202</v>
       </c>
       <c r="B21" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2880,43 +2889,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566564</v>
+        <v>566493</v>
       </c>
       <c r="R21" t="n">
-        <v>7041444</v>
+        <v>7041714</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2948,7 +2948,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3446,10 +3446,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120222903</v>
+        <v>120222990</v>
       </c>
       <c r="B26" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3462,21 +3462,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3486,10 +3486,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566505</v>
+        <v>566475</v>
       </c>
       <c r="R26" t="n">
-        <v>7041563</v>
+        <v>7041565</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3521,7 +3521,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3558,10 +3558,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120222990</v>
+        <v>120222903</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3574,21 +3574,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3598,10 +3598,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566475</v>
+        <v>566505</v>
       </c>
       <c r="R27" t="n">
-        <v>7041565</v>
+        <v>7041563</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 41505-2024 artfynd.xlsx
+++ b/artfynd/A 41505-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120222626</v>
+        <v>120222763</v>
       </c>
       <c r="B2" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566559</v>
+        <v>566538</v>
       </c>
       <c r="R2" t="n">
-        <v>7041473</v>
+        <v>7041535</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120223955</v>
+        <v>120222753</v>
       </c>
       <c r="B3" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +804,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566345</v>
+        <v>566546</v>
       </c>
       <c r="R3" t="n">
-        <v>7041782</v>
+        <v>7041554</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120222972</v>
+        <v>120222990</v>
       </c>
       <c r="B4" t="n">
-        <v>56532</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,46 +916,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566530</v>
+        <v>566475</v>
       </c>
       <c r="R4" t="n">
-        <v>7041605</v>
+        <v>7041565</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,19 +1004,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120222893</v>
+        <v>120222579</v>
       </c>
       <c r="B5" t="n">
         <v>57320</v>
@@ -1054,16 +1050,21 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566554</v>
+        <v>566558</v>
       </c>
       <c r="R5" t="n">
-        <v>7041587</v>
+        <v>7041464</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,12 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120223345</v>
+        <v>120222506</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,34 +1154,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566473</v>
+        <v>566564</v>
       </c>
       <c r="R6" t="n">
-        <v>7041726</v>
+        <v>7041444</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120223457</v>
+        <v>120222439</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,42 +1271,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566452</v>
+        <v>566548</v>
       </c>
       <c r="R7" t="n">
-        <v>7041743</v>
+        <v>7041434</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1482,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120222649</v>
+        <v>120222626</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,39 +1504,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566556</v>
+        <v>566559</v>
       </c>
       <c r="R9" t="n">
-        <v>7041534</v>
+        <v>7041473</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,12 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,22 +1588,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120223384</v>
+        <v>120223599</v>
       </c>
       <c r="B10" t="n">
-        <v>91023</v>
+        <v>91246</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,34 +1616,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>898</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566465</v>
+        <v>566435</v>
       </c>
       <c r="R10" t="n">
-        <v>7041759</v>
+        <v>7041764</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1675,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1685,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120222413</v>
+        <v>120222408</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,38 +1724,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566568</v>
+        <v>566528</v>
       </c>
       <c r="R11" t="n">
-        <v>7041467</v>
+        <v>7041423</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1801,7 +1802,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På Tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,19 +1822,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120222380</v>
+        <v>120222649</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1862,16 +1868,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566570</v>
+        <v>566556</v>
       </c>
       <c r="R12" t="n">
-        <v>7041464</v>
+        <v>7041534</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1914,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1924,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1945,10 +1956,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120223311</v>
+        <v>120222972</v>
       </c>
       <c r="B13" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,30 +1968,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1989,13 +2001,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566476</v>
+        <v>566530</v>
       </c>
       <c r="R13" t="n">
-        <v>7041727</v>
+        <v>7041605</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2024,7 +2036,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2034,7 +2046,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,22 +2061,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120223099</v>
+        <v>120223955</v>
       </c>
       <c r="B14" t="n">
-        <v>91023</v>
+        <v>97930</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2077,34 +2089,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566497</v>
+        <v>566345</v>
       </c>
       <c r="R14" t="n">
-        <v>7041610</v>
+        <v>7041782</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,7 +2152,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2146,7 +2162,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,10 +2189,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120223831</v>
+        <v>120223457</v>
       </c>
       <c r="B15" t="n">
-        <v>90600</v>
+        <v>97930</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,38 +2201,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566397</v>
+        <v>566452</v>
       </c>
       <c r="R15" t="n">
-        <v>7041615</v>
+        <v>7041743</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,7 +2268,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2258,7 +2278,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,22 +2293,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120222949</v>
+        <v>120222893</v>
       </c>
       <c r="B16" t="n">
-        <v>56524</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,16 +2321,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2318,26 +2338,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566482</v>
+        <v>566554</v>
       </c>
       <c r="R16" t="n">
-        <v>7041546</v>
+        <v>7041587</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2369,7 +2380,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,7 +2390,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,22 +2410,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120223301</v>
+        <v>120222653</v>
       </c>
       <c r="B17" t="n">
-        <v>91246</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,34 +2438,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566477</v>
+        <v>566557</v>
       </c>
       <c r="R17" t="n">
-        <v>7041729</v>
+        <v>7041495</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2481,7 +2501,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2491,7 +2511,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2518,10 +2538,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120222439</v>
+        <v>120223301</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>91246</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2530,38 +2550,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566548</v>
+        <v>566477</v>
       </c>
       <c r="R18" t="n">
-        <v>7041434</v>
+        <v>7041729</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2593,7 +2613,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2603,7 +2623,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2630,10 +2650,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120222408</v>
+        <v>120223384</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2642,43 +2662,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566528</v>
+        <v>566465</v>
       </c>
       <c r="R19" t="n">
-        <v>7041423</v>
+        <v>7041759</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2710,7 +2725,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,12 +2735,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På Tall</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2752,10 +2762,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120222506</v>
+        <v>120222949</v>
       </c>
       <c r="B20" t="n">
-        <v>57473</v>
+        <v>56524</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2768,26 +2778,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2797,14 +2807,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566564</v>
+        <v>566482</v>
       </c>
       <c r="R20" t="n">
-        <v>7041444</v>
+        <v>7041546</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2836,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2846,7 +2856,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,10 +2883,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120223202</v>
+        <v>120223831</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>90600</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2889,21 +2899,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2913,10 +2923,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566493</v>
+        <v>566397</v>
       </c>
       <c r="R21" t="n">
-        <v>7041714</v>
+        <v>7041615</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2948,7 +2958,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2958,7 +2968,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2973,22 +2983,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120222384</v>
+        <v>120223345</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2997,42 +3007,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566537</v>
+        <v>566473</v>
       </c>
       <c r="R22" t="n">
-        <v>7041443</v>
+        <v>7041726</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3064,7 +3070,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3074,7 +3080,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3101,10 +3107,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120223599</v>
+        <v>120223202</v>
       </c>
       <c r="B23" t="n">
-        <v>91246</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3113,38 +3119,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>898</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566435</v>
+        <v>566493</v>
       </c>
       <c r="R23" t="n">
-        <v>7041764</v>
+        <v>7041714</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3176,7 +3182,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3186,7 +3192,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3213,7 +3219,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120222653</v>
+        <v>120222384</v>
       </c>
       <c r="B24" t="n">
         <v>97930</v>
@@ -3248,7 +3254,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3257,10 +3263,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566557</v>
+        <v>566537</v>
       </c>
       <c r="R24" t="n">
-        <v>7041495</v>
+        <v>7041443</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3292,7 +3298,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3302,7 +3308,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3329,10 +3335,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120222763</v>
+        <v>120222413</v>
       </c>
       <c r="B25" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3341,25 +3347,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3369,10 +3375,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566538</v>
+        <v>566568</v>
       </c>
       <c r="R25" t="n">
-        <v>7041535</v>
+        <v>7041467</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3404,7 +3410,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3414,12 +3420,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3446,10 +3447,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120222990</v>
+        <v>120222471</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3462,34 +3463,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566475</v>
+        <v>566555</v>
       </c>
       <c r="R26" t="n">
-        <v>7041565</v>
+        <v>7041449</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3521,7 +3522,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3531,7 +3532,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3558,10 +3559,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120222903</v>
+        <v>120222380</v>
       </c>
       <c r="B27" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3574,34 +3575,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566505</v>
+        <v>566570</v>
       </c>
       <c r="R27" t="n">
-        <v>7041563</v>
+        <v>7041464</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3633,7 +3634,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3643,7 +3644,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3658,22 +3664,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120222753</v>
+        <v>120222903</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3686,34 +3692,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566546</v>
+        <v>566505</v>
       </c>
       <c r="R28" t="n">
-        <v>7041554</v>
+        <v>7041563</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3745,7 +3751,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3755,7 +3761,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3782,10 +3788,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120222579</v>
+        <v>120223099</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3794,43 +3800,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566558</v>
+        <v>566497</v>
       </c>
       <c r="R29" t="n">
-        <v>7041464</v>
+        <v>7041610</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3862,7 +3863,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3872,12 +3873,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4016,10 +4012,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120222471</v>
+        <v>120223311</v>
       </c>
       <c r="B31" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4028,38 +4024,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566555</v>
+        <v>566476</v>
       </c>
       <c r="R31" t="n">
-        <v>7041449</v>
+        <v>7041727</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 41505-2024 artfynd.xlsx
+++ b/artfynd/A 41505-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120222763</v>
+        <v>120223243</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>90923</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566538</v>
+        <v>566478</v>
       </c>
       <c r="R2" t="n">
-        <v>7041535</v>
+        <v>7041715</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120222753</v>
+        <v>120222990</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -828,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566546</v>
+        <v>566475</v>
       </c>
       <c r="R3" t="n">
-        <v>7041554</v>
+        <v>7041565</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120222990</v>
+        <v>120222471</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566475</v>
+        <v>566555</v>
       </c>
       <c r="R4" t="n">
-        <v>7041565</v>
+        <v>7041449</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120222579</v>
+        <v>120222506</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,27 +1027,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1061,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566558</v>
+        <v>566564</v>
       </c>
       <c r="R5" t="n">
-        <v>7041464</v>
+        <v>7041444</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120222506</v>
+        <v>120222949</v>
       </c>
       <c r="B6" t="n">
-        <v>57473</v>
+        <v>56524</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,26 +1148,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1183,14 +1177,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566564</v>
+        <v>566482</v>
       </c>
       <c r="R6" t="n">
-        <v>7041444</v>
+        <v>7041546</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120222439</v>
+        <v>120223301</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>91246</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,38 +1265,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566548</v>
+        <v>566477</v>
       </c>
       <c r="R7" t="n">
-        <v>7041434</v>
+        <v>7041729</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120223736</v>
+        <v>120222653</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,43 +1377,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566434</v>
+        <v>566557</v>
       </c>
       <c r="R8" t="n">
-        <v>7041848</v>
+        <v>7041495</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1481,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120222626</v>
+        <v>120223457</v>
       </c>
       <c r="B9" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1500,38 +1493,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566559</v>
+        <v>566452</v>
       </c>
       <c r="R9" t="n">
-        <v>7041473</v>
+        <v>7041743</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1560,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1570,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120223599</v>
+        <v>120222384</v>
       </c>
       <c r="B10" t="n">
-        <v>91246</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,34 +1613,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>898</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566435</v>
+        <v>566537</v>
       </c>
       <c r="R10" t="n">
-        <v>7041764</v>
+        <v>7041443</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1676,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,7 +1686,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,10 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120222408</v>
+        <v>120223099</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>91023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1724,43 +1725,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566528</v>
+        <v>566497</v>
       </c>
       <c r="R11" t="n">
-        <v>7041423</v>
+        <v>7041610</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1802,12 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På Tall</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120222649</v>
+        <v>120223311</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,43 +1837,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>566556</v>
+        <v>566476</v>
       </c>
       <c r="R12" t="n">
-        <v>7041534</v>
+        <v>7041727</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1924,12 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1944,22 +1929,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120222972</v>
+        <v>120222626</v>
       </c>
       <c r="B13" t="n">
-        <v>56532</v>
+        <v>90864</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1968,46 +1953,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566530</v>
+        <v>566559</v>
       </c>
       <c r="R13" t="n">
-        <v>7041605</v>
+        <v>7041473</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2036,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2046,7 +2026,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,22 +2041,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120223955</v>
+        <v>120223202</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,42 +2065,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566345</v>
+        <v>566493</v>
       </c>
       <c r="R14" t="n">
-        <v>7041782</v>
+        <v>7041714</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2152,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2162,7 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2189,10 +2165,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120223457</v>
+        <v>120222753</v>
       </c>
       <c r="B15" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2201,42 +2177,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>566452</v>
+        <v>566546</v>
       </c>
       <c r="R15" t="n">
-        <v>7041743</v>
+        <v>7041554</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2268,7 +2240,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2278,7 +2250,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2305,10 +2277,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120222893</v>
+        <v>120222413</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2317,25 +2289,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2345,10 +2317,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>566554</v>
+        <v>566568</v>
       </c>
       <c r="R16" t="n">
-        <v>7041587</v>
+        <v>7041467</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2380,7 +2352,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2390,12 +2362,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2422,10 +2389,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120222653</v>
+        <v>120222579</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2434,30 +2401,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2466,10 +2434,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>566557</v>
+        <v>566558</v>
       </c>
       <c r="R17" t="n">
-        <v>7041495</v>
+        <v>7041464</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2501,7 +2469,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2511,7 +2479,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2538,7 +2511,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120223301</v>
+        <v>120223599</v>
       </c>
       <c r="B18" t="n">
         <v>91246</v>
@@ -2574,14 +2547,14 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566477</v>
+        <v>566435</v>
       </c>
       <c r="R18" t="n">
-        <v>7041729</v>
+        <v>7041764</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,7 +2586,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2623,7 +2596,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2650,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120223384</v>
+        <v>120222439</v>
       </c>
       <c r="B19" t="n">
-        <v>91023</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2662,38 +2635,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566465</v>
+        <v>566548</v>
       </c>
       <c r="R19" t="n">
-        <v>7041759</v>
+        <v>7041434</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2725,7 +2698,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2735,7 +2708,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2762,10 +2735,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120222949</v>
+        <v>120223736</v>
       </c>
       <c r="B20" t="n">
-        <v>56524</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2778,16 +2751,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2795,26 +2768,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566482</v>
+        <v>566434</v>
       </c>
       <c r="R20" t="n">
-        <v>7041546</v>
+        <v>7041848</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2846,7 +2815,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2856,7 +2825,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2883,10 +2852,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120223831</v>
+        <v>120222893</v>
       </c>
       <c r="B21" t="n">
-        <v>90600</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2899,34 +2868,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566397</v>
+        <v>566554</v>
       </c>
       <c r="R21" t="n">
-        <v>7041615</v>
+        <v>7041587</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2958,7 +2927,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2968,7 +2937,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2995,10 +2969,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120223345</v>
+        <v>120222380</v>
       </c>
       <c r="B22" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3011,34 +2985,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>566473</v>
+        <v>566570</v>
       </c>
       <c r="R22" t="n">
-        <v>7041726</v>
+        <v>7041464</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3070,7 +3044,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3080,7 +3054,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3095,22 +3074,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120223202</v>
+        <v>120222408</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3123,34 +3102,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>566493</v>
+        <v>566528</v>
       </c>
       <c r="R23" t="n">
-        <v>7041714</v>
+        <v>7041423</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3182,7 +3166,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3192,7 +3176,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På Tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3219,10 +3208,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120222384</v>
+        <v>120222972</v>
       </c>
       <c r="B24" t="n">
-        <v>97930</v>
+        <v>56532</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3231,45 +3220,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>566537</v>
+        <v>566530</v>
       </c>
       <c r="R24" t="n">
-        <v>7041443</v>
+        <v>7041605</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3298,7 +3288,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3308,7 +3298,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3323,22 +3313,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120222413</v>
+        <v>120223384</v>
       </c>
       <c r="B25" t="n">
-        <v>91858</v>
+        <v>91023</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3347,38 +3337,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>566568</v>
+        <v>566465</v>
       </c>
       <c r="R25" t="n">
-        <v>7041467</v>
+        <v>7041759</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3410,7 +3400,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3420,7 +3410,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3435,22 +3425,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120222471</v>
+        <v>120223345</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3463,34 +3453,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>566555</v>
+        <v>566473</v>
       </c>
       <c r="R26" t="n">
-        <v>7041449</v>
+        <v>7041726</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3522,7 +3512,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3532,7 +3522,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3559,10 +3549,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120222380</v>
+        <v>120222903</v>
       </c>
       <c r="B27" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3575,34 +3565,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>566570</v>
+        <v>566505</v>
       </c>
       <c r="R27" t="n">
-        <v>7041464</v>
+        <v>7041563</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3634,7 +3624,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3644,12 +3634,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3664,22 +3649,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120222903</v>
+        <v>120223831</v>
       </c>
       <c r="B28" t="n">
-        <v>82321</v>
+        <v>90600</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3692,21 +3677,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3716,10 +3701,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>566505</v>
+        <v>566397</v>
       </c>
       <c r="R28" t="n">
-        <v>7041563</v>
+        <v>7041615</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3751,7 +3736,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3761,7 +3746,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3776,22 +3761,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120223099</v>
+        <v>120223955</v>
       </c>
       <c r="B29" t="n">
-        <v>91023</v>
+        <v>97930</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3804,34 +3789,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1209</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>566497</v>
+        <v>566345</v>
       </c>
       <c r="R29" t="n">
-        <v>7041610</v>
+        <v>7041782</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3863,7 +3852,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3873,7 +3862,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3900,10 +3889,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120223243</v>
+        <v>120222649</v>
       </c>
       <c r="B30" t="n">
-        <v>90923</v>
+        <v>57320</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3912,38 +3901,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2062</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>566478</v>
+        <v>566556</v>
       </c>
       <c r="R30" t="n">
-        <v>7041715</v>
+        <v>7041534</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3975,7 +3969,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3985,7 +3979,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4000,22 +3999,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120223311</v>
+        <v>120222763</v>
       </c>
       <c r="B31" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4024,42 +4023,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>566476</v>
+        <v>566538</v>
       </c>
       <c r="R31" t="n">
-        <v>7041727</v>
+        <v>7041535</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4091,7 +4086,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4101,7 +4096,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4116,12 +4116,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 41505-2024 artfynd.xlsx
+++ b/artfynd/A 41505-2024 artfynd.xlsx
@@ -1941,10 +1941,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120222626</v>
+        <v>120223202</v>
       </c>
       <c r="B13" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,34 +1957,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Kolmyrberget, Kolmyrberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>566559</v>
+        <v>566493</v>
       </c>
       <c r="R13" t="n">
-        <v>7041473</v>
+        <v>7041714</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,10 +2053,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120223202</v>
+        <v>120222626</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,34 +2069,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kolmyrberget, Kolmyrberget, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>566493</v>
+        <v>566559</v>
       </c>
       <c r="R14" t="n">
-        <v>7041714</v>
+        <v>7041473</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2511,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120223599</v>
+        <v>120223736</v>
       </c>
       <c r="B18" t="n">
-        <v>91246</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2523,38 +2523,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>566435</v>
+        <v>566434</v>
       </c>
       <c r="R18" t="n">
-        <v>7041764</v>
+        <v>7041848</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,7 +2591,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2596,7 +2601,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,10 +2628,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120222439</v>
+        <v>120222893</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,21 +2644,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2663,10 +2668,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>566548</v>
+        <v>566554</v>
       </c>
       <c r="R19" t="n">
-        <v>7041434</v>
+        <v>7041587</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2698,7 +2703,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2708,7 +2713,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2723,22 +2733,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120223736</v>
+        <v>120222439</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2751,39 +2761,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
+          <t>Dalsberget, Dalsberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>566434</v>
+        <v>566548</v>
       </c>
       <c r="R20" t="n">
-        <v>7041848</v>
+        <v>7041434</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2815,7 +2820,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2825,7 +2830,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,10 +2857,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120222893</v>
+        <v>120223599</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>91246</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2864,38 +2869,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Dalsberget, Dalsberget, Ång</t>
+          <t>Herrpelltjärnkullen, Herrpelltjärnkullen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>566554</v>
+        <v>566435</v>
       </c>
       <c r="R21" t="n">
-        <v>7041587</v>
+        <v>7041764</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2927,7 +2932,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2937,12 +2942,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:03</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,12 +2957,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
